--- a/data/trans_orig/IP31C_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74607</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108149</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111752</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>94285</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39310</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>121547</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>118981</t>
+          <t>91995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111618</t>
+          <t>80294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>96341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>213266</t>
+          <t>200145</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135275</t>
+          <t>188365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240902</t>
+          <t>206725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84631</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111632</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3192</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2416</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7007</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55743</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52031</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>54249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51065</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>52827</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>49541</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54112</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>62866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>58141</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>64633</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>89,96%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>182</t>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>117116</t>
+          <t>108571</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113235</t>
+          <t>104620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119530</t>
+          <t>110765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4654</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4487</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1858,107 +1858,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60449</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54712</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>64928</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>53846</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46697</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65438</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70629</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>119284</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109156</t>
+          <t>105269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127652</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>997</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>847</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8370</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13640</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>14495</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9635</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21617</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32764</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,74 +2544,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>35385</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31805</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37577</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>36622</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>32944</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>38862</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>130</t>
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>70822</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66972</t>
+          <t>67420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73019</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3418</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>3728</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>2974</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -2770,107 +2770,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3180</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3356</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6632</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,74 +3000,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>43622</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>40848</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>43651</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>40018</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>44286</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>53782</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -3075,27 +3075,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>97404</t>
+          <t>90860</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>88435</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3226,107 +3226,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3442</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4268</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>121519</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>112815</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>128063</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>80,75%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>111593</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>105065</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>116388</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>85,4%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>135514</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125384</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141750</t>
+          <t>113698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>247106</t>
+          <t>230718</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>236870</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256173</t>
+          <t>239588</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1443</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>4725</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>4458</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>755</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17286</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11151</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>26310</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>9991</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>5691</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>15857</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3912,72 +3912,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>123037</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>112272</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>132295</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>71,66%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>84,44%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>107291</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>99189</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>113613</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>77,64%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>121817</t>
+          <t>114643</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>112020</t>
+          <t>105774</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>129900</t>
+          <t>121926</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>229107</t>
+          <t>237680</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>216616</t>
+          <t>224463</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>249200</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -4025,107 +4025,107 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>2428</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>3039</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4138,72 +4138,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>33132</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>24086</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>44351</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>28,31%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>20470</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>14148</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>28572</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>31346</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>44084</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>68605</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4368,72 +4368,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>611755</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>594838</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>624783</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>839</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>570485</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>478345</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>600018</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>669628</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>653190</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>683723</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1240114</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1143772</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1271892</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -4481,72 +4481,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>140049</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>65760</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>53259</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>81355</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>48040</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>36228</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>61083</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>99650</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>137397</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
